--- a/resultados/terraroxa/erros_varredura.xlsx
+++ b/resultados/terraroxa/erros_varredura.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F5"/>
+  <dimension ref="A1:F31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -560,6 +560,734 @@
         </is>
       </c>
     </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>terraroxa</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>https://www.terraroxa.pr.gov.br/autoatendimento/servicos/emissao-da-certidao-de-responsabilidade-tecnica</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" t="n">
+        <v>5</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>2026-08-20 11:12:47</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>terraroxa</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>https://www.terraroxa.pr.gov.br/autoatendimento/servicos/autenticidade-de-certidao-negativa-de-debitos/detalhar/1</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" t="n">
+        <v>4</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>2026-08-20 11:43:49</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>terraroxa</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>https://www.terraroxa.pr.gov.br/autoatendimento/servicos/gerenciamento-de-empresas/detalhar/1</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" t="n">
+        <v>4</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>2026-08-20 11:44:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>terraroxa</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>https://www.terraroxa.pr.gov.br/autoatendimento/servicos/denuncias-ambientais/detalhar/1</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" t="n">
+        <v>4</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>2026-08-20 11:44:40</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>terraroxa</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>https://www.terraroxa.pr.gov.br/autoatendimento/servicos/consulta-de-notificacoes-ambientais/detalhar/1</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" t="n">
+        <v>4</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>2026-08-20 11:44:42</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>terraroxa</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>https://www.terraroxa.pr.gov.br/autoatendimento/servicos/avaliacao-de-estagio-probatorio/detalhar/1</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>0</v>
+      </c>
+      <c r="E11" t="n">
+        <v>4</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>2026-08-20 11:46:59</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>terraroxa</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>https://www.terraroxa.pr.gov.br/autoatendimento/servicos/extrato-de-emprestimos-consignados/detalhar/1</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>0</v>
+      </c>
+      <c r="E12" t="n">
+        <v>4</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>2026-08-20 11:50:13</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>terraroxa</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>https://www.terraroxa.pr.gov.br/autoatendimento/servicos/solicitacao-de-emissao-de-inutilizacao-de-medicamento/detalhar/1</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>0</v>
+      </c>
+      <c r="E13" t="n">
+        <v>4</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>2026-08-20 11:52:21</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>terraroxa</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>https://terraroxa.atende.net/cidadao/pagina/o-que-e-sicaf?pg=transparencia</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>0</v>
+      </c>
+      <c r="E14" t="n">
+        <v>4</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>2026-08-20 11:54:08</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>terraroxa</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>https://terraroxa.atende.net/cidadao/pagina/insumos-recebidos?pg=transparencia</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>0</v>
+      </c>
+      <c r="E15" t="n">
+        <v>4</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>2026-08-20 11:55:31</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>terraroxa</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>https://terraroxa.atende.net/cidadao/pagina/denuncias?pg=transparencia</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>0</v>
+      </c>
+      <c r="E16" t="n">
+        <v>4</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>2026-08-20 11:55:32</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>terraroxa</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>https://terraroxa.atende.net/cidadao/pagina/boletim-coronavirus?pg=transparencia</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>0</v>
+      </c>
+      <c r="E17" t="n">
+        <v>4</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>2026-08-20 11:55:36</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>terraroxa</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>https://terraroxa.atende.net/cidadao/noticia/autoatendimento/servicos/autoatendimento/servicos/consulta-de-processo-digital?pg=transparencia</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>0</v>
+      </c>
+      <c r="E18" t="n">
+        <v>4</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>2026-08-20 11:55:40</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>terraroxa</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>https://terraroxa.atende.net/cidadao/video/autoatendimento/servicos/consulta-de-processo-digital?pg=transparencia</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>0</v>
+      </c>
+      <c r="E19" t="n">
+        <v>4</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>2026-08-20 11:56:33</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>terraroxa</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>https://terraroxa.atende.net/autoatendimento/servicos/relatorio-gerencial-de-ferias/detalhar/1</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>0</v>
+      </c>
+      <c r="E20" t="n">
+        <v>5</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>2026-08-20 12:04:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>terraroxa</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>https://terraroxa.atende.net/autoatendimento/servicos/minhas-auditorias/detalhar/1</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>0</v>
+      </c>
+      <c r="E21" t="n">
+        <v>5</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>2026-08-20 12:04:27</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>terraroxa</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>https://terraroxa.atende.net/autoatendimento/servicos/solicitacao-de-emissao-de-inutilizacao-de-medicamento/detalhar/1</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>0</v>
+      </c>
+      <c r="E22" t="n">
+        <v>5</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>2026-08-20 12:06:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>terraroxa</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>https://terraroxa.atende.net/autoatendimento/servicos/solicitacao-de-participacao-em-evento/detalhar/1</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>0</v>
+      </c>
+      <c r="E23" t="n">
+        <v>5</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>2026-08-20 12:07:07</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>terraroxa</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>https://www.terraroxa.pr.gov.br/autoatendimento/servicos/emissao-de-alvara-sanitario</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>0</v>
+      </c>
+      <c r="E24" t="n">
+        <v>5</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>2026-08-20 12:07:14</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>terraroxa</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>https://terraroxa.atende.net/cidadao/pagina/autoatendimento/servicos/autoatendimento/servicos/consulta-de-processo-digital?pg=transparencia</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>0</v>
+      </c>
+      <c r="E25" t="n">
+        <v>5</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>2026-08-20 12:08:31</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>terraroxa</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>https://terraroxa.atende.net/cidadao/noticia/autoatendimento/servicos/autoatendimento/servicos/?pg=transparencia</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>0</v>
+      </c>
+      <c r="E26" t="n">
+        <v>5</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>2026-08-20 12:08:33</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>terraroxa</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>https://www.terraroxa.pr.gov.br/cidadao/acesso-informacao/autoatendimento/servicos/autoatendimento/servicos/autoatendimento/servicos/consulta-de-processo-digital?pg=transparencia</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>0</v>
+      </c>
+      <c r="E27" t="n">
+        <v>5</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>2026-08-20 12:09:52</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>terraroxa</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>https://www.terraroxa.pr.gov.br/cidadao/video/autoatendimento/servicos/autoatendimento/servicos/autoatendimento/servicos/consulta-de-processo-digital?pg=transparencia</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>0</v>
+      </c>
+      <c r="E28" t="n">
+        <v>5</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>2026-08-20 12:10:01</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>terraroxa</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>https://www.terraroxa.pr.gov.br/cidadao/noticia/edital-de-chamanento-publico-de-n-0032026?pg=transparencia</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>0</v>
+      </c>
+      <c r="E29" t="n">
+        <v>6</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>2026-08-20 12:12:31</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>terraroxa</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>https://www.terraroxa.pr.gov.br/cidadao/video/autoatendimento/servicos/autoatendimento/servicos/autoatendimento/servicos/autoatendimento/servicos/consulta-de-processo-digital?pg=transparencia</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>0</v>
+      </c>
+      <c r="E30" t="n">
+        <v>6</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>2026-08-20 12:12:40</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>terraroxa</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>https://www.terraroxa.pr.gov.br/cidadao/pagina/autoatendimento/servicos/autoatendimento/servicos/autoatendimento/servicos/autoatendimento/servicos/?pg=transparencia</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>0</v>
+      </c>
+      <c r="E31" t="n">
+        <v>7</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>2026-08-20 12:12:41</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
